--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -1,60 +1,208 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85FBDE8D-5AFF-41F3-B8BD-1D0294119019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MapConfig" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MapConfig" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="40">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>width_cells</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>地图ID</t>
+  </si>
+  <si>
+    <t>地图名称</t>
+  </si>
+  <si>
+    <t>默认地图一</t>
+  </si>
+  <si>
+    <t>默认地图二</t>
+  </si>
+  <si>
+    <t>spatial_mode</t>
+  </si>
+  <si>
+    <t>depth_cells</t>
+  </si>
+  <si>
+    <t>grid_cell_size_meters</t>
+  </si>
+  <si>
+    <t>spawn_x</t>
+  </si>
+  <si>
+    <t>spawn_y</t>
+  </si>
+  <si>
+    <t>spawn_z</t>
+  </si>
+  <si>
+    <t>spawn_yaw</t>
+  </si>
+  <si>
+    <t>aoi_cell_size_meters</t>
+  </si>
+  <si>
+    <t>navigation_asset</t>
+  </si>
+  <si>
+    <t>navigation_version</t>
+  </si>
+  <si>
+    <t>navigation_hash</t>
+  </si>
+  <si>
+    <t>SpatialMode</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>空间模式</t>
+  </si>
+  <si>
+    <t>地图X轴Cell数量</t>
+  </si>
+  <si>
+    <t>地图Z轴Cell数量</t>
+  </si>
+  <si>
+    <t>每格米数</t>
+  </si>
+  <si>
+    <t>出生点X（米）</t>
+  </si>
+  <si>
+    <t>出生点Y（米）</t>
+  </si>
+  <si>
+    <t>出生点Z（米）</t>
+  </si>
+  <si>
+    <t>出生朝向Yaw（弧度）</t>
+  </si>
+  <si>
+    <t>AOI Cell边长（米）</t>
+  </si>
+  <si>
+    <t>导航资源标识</t>
+  </si>
+  <si>
+    <t>导航资源版本</t>
+  </si>
+  <si>
+    <t>导航资源SHA-256</t>
+  </si>
+  <si>
+    <t>Grid2D</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,92 +219,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -444,217 +533,285 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>width_cells</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>height_cells</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>spawn_cell_x</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>spawn_cell_y</t>
-        </is>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>6</v>
+      </c>
+      <c r="N2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>##</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>地图ID</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>地图名称</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>地图横向Cell数量</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>地图纵向Cell数量</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>默认出生Cell X</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>默认出生Cell Y</t>
-        </is>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="n">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>默认地图一</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5">
         <v>128</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5">
         <v>128</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5">
         <v>0</v>
       </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>8</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="B6" t="n">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>默认地图二</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6">
         <v>128</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6">
         <v>128</v>
       </c>
-      <c r="F6" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
         <v>8</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="10.6640625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1009,66 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3D导航灰盒</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NavMesh3D</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>48</v>
+      </c>
+      <c r="F9" t="n">
+        <v>48</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>navigation/maps/demo_3d/generated/navigation.bin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>demo-3d-v1</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>94af0f91826b6c08d72f2402cd06383847cf8ceb7d87d9dd9067a2b9c862f304</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>

--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -1054,12 +1054,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>demo-3d-v1</t>
+          <t>demo-3d-v2</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>94af0f91826b6c08d72f2402cd06383847cf8ceb7d87d9dd9067a2b9c862f304</t>
+          <t>1844ce35706c008f494bc74b6a6c55105e5da3d3fc104634e9c8726daab67421</t>
         </is>
       </c>
       <c r="P9" t="n">

--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D12BD7E-F00A-468E-A891-C94991B5AB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62ADCCE-0261-44E0-88DE-EED0A724D155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="1260" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapConfig" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
   <si>
     <t>##var</t>
   </si>
@@ -184,6 +184,26 @@
   </si>
   <si>
     <t>1844ce35706c008f494bc74b6a6c55105e5da3d3fc104634e9c8726daab67421</t>
+  </si>
+  <si>
+    <t>Starter Boss试炼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NavMesh3D</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>navigation/maps/demo_3d/generated/navigation.bin</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>demo-3d-v2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>1844ce35706c008f494bc74b6a6c55105e5da3d3fc104634e9c8726daab67421</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -573,7 +593,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1018,6 +1038,56 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>200</v>
+      </c>
+      <c r="C10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <v>60</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>-3</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>-18</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" t="s">
+        <v>56</v>
+      </c>
+      <c r="O10" t="s">
+        <v>57</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62ADCCE-0261-44E0-88DE-EED0A724D155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34652EDD-7EAB-4B61-B357-2947A58E6721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapConfig" sheetId="1" r:id="rId1"/>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5">
         <v>10000</v>

--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34652EDD-7EAB-4B61-B357-2947A58E6721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A272B-B9A9-4642-AD5D-30A12D8F4E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1896" yWindow="2004" windowWidth="23700" windowHeight="9696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapConfig" sheetId="1" r:id="rId1"/>
@@ -894,7 +894,7 @@
         <v>22</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>1.5707963</v>
       </c>
       <c r="L6">
         <v>1</v>

--- a/game_config/Datas/MapConfig.xlsx
+++ b/game_config/Datas/MapConfig.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitee\TiangZ\game_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TiangZ\outputs\wow335-aoi-20260903\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A9A272B-B9A9-4642-AD5D-30A12D8F4E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{513B88A1-8134-4B39-A6E6-87AB72C0DD5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1896" yWindow="2004" windowWidth="23700" windowHeight="9696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MapConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -204,6 +199,9 @@
   <si>
     <t>1844ce35706c008f494bc74b6a6c55105e5da3d3fc104634e9c8726daab67421</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>WoW335 血精灵新手区</t>
   </si>
 </sst>
 </file>
@@ -593,26 +591,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.69140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.4609375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.3046875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.21875" customWidth="1"/>
-    <col min="14" max="14" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="15.69140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.23046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.23046875" customWidth="1"/>
+    <col min="14" max="14" width="20.4609375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.765625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -665,7 +663,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -718,7 +716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
@@ -771,7 +769,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>26</v>
       </c>
@@ -824,7 +822,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1</v>
       </c>
@@ -865,7 +863,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2</v>
       </c>
@@ -906,7 +904,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>1015</v>
       </c>
@@ -947,7 +945,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>1020</v>
       </c>
@@ -988,7 +986,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>100</v>
       </c>
@@ -1038,7 +1036,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>200</v>
       </c>
@@ -1086,6 +1084,47 @@
       </c>
       <c r="Q10">
         <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B11">
+        <v>201</v>
+      </c>
+      <c r="C11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11">
+        <v>720</v>
+      </c>
+      <c r="F11">
+        <v>1200</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>
